--- a/Master/DS User.xlsx
+++ b/Master/DS User.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.83203125" customWidth="1" min="1" max="1"/>
@@ -3864,6 +3864,126 @@
         <v>0</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>audit1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AUDIT1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn An (Audit 1)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>AUDITOR</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Miền Nam (Văn Phòng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>audit2</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AUDIT2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Trần Thị Bích (Trade Mkt 2)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>AUDITOR</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Miền Bắc (Văn Phòng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>audit3</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AUDIT3</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Lê Hoàng Nam (Sales Cap 3)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>AUDITOR</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Miền Trung (Văn Phòng)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
